--- a/assets/docs/Synthese_Epreuve_E5_2025.xlsx
+++ b/assets/docs/Synthese_Epreuve_E5_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilan.dahan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilan.dahan/Desktop/iPortfolio/assets/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6850D156-0183-914C-A126-2BB4BC47F773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0430B8D2-2B88-9F4F-8838-AA592888496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>SESSION 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> SLAM</t>
   </si>
   <si>
@@ -178,6 +175,21 @@
   </si>
   <si>
     <t>NOM et prénom : Dahan Ilan</t>
+  </si>
+  <si>
+    <t>Refonte et optumisation du site web de l'entreprise</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Creation de base de donnée</t>
+  </si>
+  <si>
+    <t>Devlopement de script pyhton</t>
+  </si>
+  <si>
+    <t>09-2024-05-2025</t>
   </si>
 </sst>
 </file>
@@ -187,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -255,6 +267,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -655,7 +677,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -720,9 +742,65 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -747,61 +825,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1121,81 +1152,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="29" t="s">
+      <c r="A3" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="30"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="50"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="A5" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1218,8 +1249,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="32"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1275,16 +1306,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="34"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1323,24 +1354,24 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>30</v>
+      <c r="G9" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1380,24 +1411,24 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="17"/>
-      <c r="D10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>30</v>
+      <c r="D10" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1437,22 +1468,22 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>30</v>
+      <c r="E11" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1492,25 +1523,23 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>27</v>
-      </c>
+      <c r="E12" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="53"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1548,25 +1577,27 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="49" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>27</v>
+      <c r="D13" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1605,14 +1636,26 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
+      <c r="A14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
+      <c r="F14" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="53"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1650,14 +1693,22 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="D15" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="F15" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="53"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1702,7 +1753,7 @@
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="53"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1747,7 +1798,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="53"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1792,7 +1843,7 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="53"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1830,16 +1881,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1877,23 +1928,25 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>27</v>
+      <c r="D20" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -2202,16 +2255,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2249,23 +2302,25 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="45" t="s">
-        <v>28</v>
+      <c r="A28" s="23" t="s">
+        <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
+      <c r="D28" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="E28" s="17"/>
-      <c r="F28" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>27</v>
+      <c r="F28" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="52" t="s">
+        <v>26</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -2304,21 +2359,23 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="45" t="s">
-        <v>38</v>
+      <c r="A29" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="17"/>
+        <v>32</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>26</v>
+      </c>
       <c r="E29" s="17"/>
-      <c r="F29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="17"/>
+      <c r="F29" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="52"/>
       <c r="H29" s="18"/>
       <c r="I29"/>
       <c r="J29"/>
@@ -2357,22 +2414,24 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="50" t="s">
-        <v>39</v>
+      <c r="A30" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>26</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="17" t="s">
-        <v>27</v>
+      <c r="G30" s="52" t="s">
+        <v>26</v>
       </c>
       <c r="H30" s="18"/>
       <c r="I30"/>
@@ -2412,11 +2471,17 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="11"/>
+      <c r="A31" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="B31" s="10"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="D31" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>26</v>
+      </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
       <c r="H31" s="18"/>
@@ -2594,6 +2659,11 @@
     <row r="79" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
@@ -2601,11 +2671,6 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/docs/Synthese_Epreuve_E5_2025.xlsx
+++ b/assets/docs/Synthese_Epreuve_E5_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilan.dahan/Desktop/iPortfolio/assets/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0430B8D2-2B88-9F4F-8838-AA592888496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD470323-C2F5-AA4B-9717-10025E85A710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="45">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -750,6 +750,42 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -765,9 +801,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -800,39 +833,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1152,56 +1152,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="31"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="49" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="50"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1211,22 +1211,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="53"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="49" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1249,8 +1249,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="39"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1306,16 +1306,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="34"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="45"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1360,17 +1360,17 @@
         <v>32</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52" t="s">
+      <c r="D9" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="28" t="s">
         <v>29</v>
       </c>
       <c r="I9"/>
@@ -1417,17 +1417,17 @@
         <v>32</v>
       </c>
       <c r="C10" s="17"/>
-      <c r="D10" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52" t="s">
+      <c r="D10" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="53" t="s">
+      <c r="H10" s="28" t="s">
         <v>29</v>
       </c>
       <c r="I10"/>
@@ -1475,14 +1475,14 @@
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52" t="s">
+      <c r="E11" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="53" t="s">
+      <c r="H11" s="28" t="s">
         <v>29</v>
       </c>
       <c r="I11"/>
@@ -1530,16 +1530,18 @@
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="53"/>
+      <c r="E12" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>29</v>
+      </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1584,19 +1586,19 @@
         <v>36</v>
       </c>
       <c r="C13" s="17"/>
-      <c r="D13" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="53" t="s">
+      <c r="D13" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="28" t="s">
         <v>26</v>
       </c>
       <c r="I13"/>
@@ -1642,20 +1644,20 @@
       <c r="B14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="52" t="s">
+      <c r="C14" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="27" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="17"/>
-      <c r="F14" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="53"/>
+      <c r="F14" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="28"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1700,15 +1702,15 @@
         <v>44</v>
       </c>
       <c r="C15" s="17"/>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="27" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="17"/>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="27" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="17"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="28"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1753,7 +1755,7 @@
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="28"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1798,7 +1800,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="28"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1843,7 +1845,7 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="28"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1881,16 +1883,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1935,17 +1937,17 @@
         <v>25</v>
       </c>
       <c r="C20" s="17"/>
-      <c r="D20" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="53" t="s">
+      <c r="D20" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="28" t="s">
         <v>26</v>
       </c>
       <c r="I20"/>
@@ -2255,16 +2257,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2309,17 +2311,17 @@
         <v>32</v>
       </c>
       <c r="C28" s="17"/>
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="27" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="17"/>
-      <c r="F28" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="18" t="s">
+      <c r="F28" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="28" t="s">
         <v>26</v>
       </c>
       <c r="I28"/>
@@ -2365,18 +2367,20 @@
       <c r="B29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="52" t="s">
+      <c r="C29" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="27" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="17"/>
-      <c r="F29" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="52"/>
-      <c r="H29" s="18"/>
+      <c r="F29" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="27"/>
+      <c r="H29" s="28" t="s">
+        <v>26</v>
+      </c>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2420,20 +2424,22 @@
       <c r="B30" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="52" t="s">
+      <c r="C30" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="18"/>
+      <c r="G30" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>26</v>
+      </c>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2476,15 +2482,17 @@
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="51" t="s">
+      <c r="D31" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="26" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="18"/>
+      <c r="H31" s="28" t="s">
+        <v>26</v>
+      </c>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2659,11 +2667,6 @@
     <row r="79" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
@@ -2671,6 +2674,11 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/assets/docs/Synthese_Epreuve_E5_2025.xlsx
+++ b/assets/docs/Synthese_Epreuve_E5_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilan.dahan/Desktop/iPortfolio/assets/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD470323-C2F5-AA4B-9717-10025E85A710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4788225-44C6-7B42-B076-5A2889B3864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -108,9 +108,6 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -126,15 +123,9 @@
     <t>Centre de formation :Ort montreuil</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :https://portfolioilandahan.netlify.app/</t>
-  </si>
-  <si>
     <t>Coffre-fort de mots de passe en Python</t>
   </si>
   <si>
-    <t>05-2025 - 06-2026</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -153,21 +144,9 @@
     <t>Développement d’un portfolio personnel</t>
   </si>
   <si>
-    <t>EN COURS</t>
-  </si>
-  <si>
-    <t>12-2025 - 03-2026</t>
-  </si>
-  <si>
-    <t>Développement d’un site de réservation pour un restaurant (projet réel en production)</t>
-  </si>
-  <si>
     <t>Création d’une application de gestion de cérémonies (Python/Flask)</t>
   </si>
   <si>
-    <t>08-2025 - 09-2025</t>
-  </si>
-  <si>
     <t>Organisation et gestion de l’environnement serveur(rangement, droits)</t>
   </si>
   <si>
@@ -177,19 +156,19 @@
     <t>NOM et prénom : Dahan Ilan</t>
   </si>
   <si>
-    <t>Refonte et optumisation du site web de l'entreprise</t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
-    <t>Creation de base de donnée</t>
-  </si>
-  <si>
-    <t>Devlopement de script pyhton</t>
-  </si>
-  <si>
-    <t>09-2024-05-2025</t>
+    <t>N° candidat : 2148395477</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio :https://ilan-dahan.fr</t>
+  </si>
+  <si>
+    <t>Développement d’un site de réservation pour un restaurant</t>
+  </si>
+  <si>
+    <t>Refonte et optumisation du site web de l'entreprise(wordpress)</t>
   </si>
 </sst>
 </file>
@@ -700,12 +679,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -833,6 +806,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1142,7 +1121,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ79"/>
+  <dimension ref="A1:AQ77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="70.5" style="1" customWidth="1"/>
@@ -1152,82 +1131,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="29"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="37"/>
+      <c r="A3" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="35"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="14" t="s">
+      <c r="A4" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="21" t="s">
-        <v>21</v>
+      <c r="G4" s="13"/>
+      <c r="H4" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="53"/>
+      <c r="A5" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="51"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>18</v>
+      <c r="B6" s="47" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1249,24 +1228,24 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="40"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="53" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1306,16 +1285,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="45"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="43"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1353,25 +1332,23 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="27" t="s">
+      <c r="A9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>29</v>
+      <c r="G9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1410,25 +1387,21 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="27" t="s">
+      <c r="A10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>29</v>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1467,23 +1440,23 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="27" t="s">
+      <c r="A11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>29</v>
+      <c r="H11" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1522,25 +1495,23 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="27" t="s">
+      <c r="A12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>26</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1579,27 +1550,25 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>26</v>
+      <c r="A13" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1638,26 +1607,14 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="28"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="26"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1695,22 +1652,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="28"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="26"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1748,14 +1697,14 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="11"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="28"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="26"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1792,15 +1741,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="28"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+      <c r="A17" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1838,14 +1789,22 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="11"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="28"/>
+      <c r="A18" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26" t="s">
+        <v>23</v>
+      </c>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1882,17 +1841,15 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A19" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1930,26 +1887,14 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>26</v>
-      </c>
+      <c r="A20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1987,14 +1932,14 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="11"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="16"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2032,14 +1977,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="11"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2077,14 +2022,14 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="11"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2122,14 +2067,14 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="11"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2166,15 +2111,17 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="11"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+      <c r="A25" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="38"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2212,14 +2159,22 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
+      <c r="A26" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26" t="s">
+        <v>23</v>
+      </c>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2256,17 +2211,23 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26" t="s">
+        <v>23</v>
+      </c>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2305,24 +2266,20 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="28" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="15"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -2361,25 +2318,21 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28" t="s">
-        <v>26</v>
+      <c r="B29" s="8"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -2417,29 +2370,15 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>26</v>
-      </c>
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="17"/>
-      <c r="G30" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>26</v>
-      </c>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2476,23 +2415,15 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="28" t="s">
-        <v>26</v>
-      </c>
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A31" s="5"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2529,111 +2460,23 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-      <c r="S32"/>
-      <c r="T32"/>
-      <c r="U32"/>
-      <c r="V32"/>
-      <c r="W32"/>
-      <c r="X32"/>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32"/>
-      <c r="AB32"/>
-      <c r="AC32"/>
-      <c r="AD32"/>
-      <c r="AE32"/>
-      <c r="AF32"/>
-      <c r="AG32"/>
-      <c r="AH32"/>
-      <c r="AI32"/>
-      <c r="AJ32"/>
-      <c r="AK32"/>
-      <c r="AL32"/>
-      <c r="AM32"/>
-      <c r="AN32"/>
-      <c r="AO32"/>
-      <c r="AP32"/>
-      <c r="AQ32"/>
-    </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A33" s="5"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
-      <c r="AG33"/>
-      <c r="AH33"/>
-      <c r="AI33"/>
-      <c r="AJ33"/>
-      <c r="AK33"/>
-      <c r="AL33"/>
-      <c r="AM33"/>
-      <c r="AN33"/>
-      <c r="AO33"/>
-      <c r="AP33"/>
-      <c r="AQ33"/>
-    </row>
-    <row r="34" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.15"/>
@@ -2663,15 +2506,13 @@
     <row r="75" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="76" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="77" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>

--- a/assets/docs/Synthese_Epreuve_E5_2025.xlsx
+++ b/assets/docs/Synthese_Epreuve_E5_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilan.dahan/Desktop/iPortfolio/assets/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4788225-44C6-7B42-B076-5A2889B3864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35F8EE4-9346-6D48-8F27-BB1CFEDCD09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -169,6 +169,27 @@
   </si>
   <si>
     <t>Refonte et optumisation du site web de l'entreprise(wordpress)</t>
+  </si>
+  <si>
+    <t>09/25/en cours</t>
+  </si>
+  <si>
+    <t>11/25-03/26</t>
+  </si>
+  <si>
+    <t>09/25-12/25</t>
+  </si>
+  <si>
+    <t>01/25-07/25</t>
+  </si>
+  <si>
+    <t>12/25-en cous</t>
+  </si>
+  <si>
+    <t>09/25-en cours</t>
+  </si>
+  <si>
+    <t>01/25-02/25</t>
   </si>
 </sst>
 </file>
@@ -265,7 +286,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -366,21 +387,6 @@
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
@@ -682,136 +688,138 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1131,81 +1139,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="34" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="35"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="31"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="12" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="19" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1228,24 +1236,24 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="40"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="52" t="s">
+      <c r="A7" s="36"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="49" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1285,16 +1293,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1335,21 +1343,19 @@
       <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="25" t="s">
+      <c r="B9" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>26</v>
-      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="53"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1390,19 +1396,19 @@
       <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="25" t="s">
+      <c r="B10" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26" t="s">
-        <v>26</v>
-      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="53"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1443,19 +1449,19 @@
       <c r="A11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="25" t="s">
+      <c r="B11" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="53" t="s">
         <v>26</v>
       </c>
       <c r="I11"/>
@@ -1498,19 +1504,21 @@
       <c r="A12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="25" t="s">
+      <c r="B12" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="53" t="s">
         <v>26</v>
       </c>
       <c r="I12"/>
@@ -1550,24 +1558,26 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="25" t="s">
+      <c r="B13" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="53" t="s">
         <v>23</v>
       </c>
       <c r="I13"/>
@@ -1608,13 +1618,13 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="9"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="26"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="22"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1653,13 +1663,13 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="26"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="22"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1698,13 +1708,13 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="26"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="22"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1742,16 +1752,16 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="46"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="42"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1789,22 +1799,26 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="25" t="s">
+      <c r="B18" s="19">
+        <v>45778</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25" t="s">
+      <c r="D18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="25"/>
-      <c r="H18" s="26" t="s">
+      <c r="E18" s="21"/>
+      <c r="F18" s="21" t="s">
         <v>23</v>
       </c>
+      <c r="G18" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="22"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1844,12 +1858,12 @@
     <row r="19" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="9"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1889,12 +1903,12 @@
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="9"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1934,12 +1948,12 @@
     <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="9"/>
       <c r="B21" s="8"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="14"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1979,12 +1993,12 @@
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9"/>
       <c r="B22" s="8"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2024,12 +2038,12 @@
     <row r="23" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="9"/>
       <c r="B23" s="8"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2069,12 +2083,12 @@
     <row r="24" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2112,16 +2126,16 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="34"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2159,22 +2173,22 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="25" t="s">
+      <c r="B26" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="25" t="s">
+      <c r="E26" s="13"/>
+      <c r="F26" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2212,22 +2226,22 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="25" t="s">
+      <c r="B27" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2265,22 +2279,22 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25" t="s">
+      <c r="B28" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2321,19 +2335,19 @@
       <c r="A29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="25" t="s">
+      <c r="B29" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="26" t="s">
-        <v>23</v>
-      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="22"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2371,14 +2385,14 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
